--- a/backtest_runs/20260410_193731/by_symbol/NITGETF/NITGETF.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/NITGETF/NITGETF.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-1357.650000000009</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>100784.42</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>100784.42</v>
@@ -771,7 +771,7 @@
         <v>-1961.050000000017</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>98823.36999999998</v>
@@ -817,7 +817,7 @@
         <v>-2534.279999999989</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>96289.08999999998</v>
@@ -863,7 +863,7 @@
         <v>-603.4000000000086</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>95685.68999999997</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>95685.68999999997</v>
@@ -1047,7 +1047,7 @@
         <v>-1961.049999999996</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>97284.69999999998</v>
@@ -1185,7 +1185,7 @@
         <v>-241.3599999999948</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>101176.63</v>
@@ -1231,7 +1231,7 @@
         <v>-4616.010000000004</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>96560.62</v>
@@ -1277,7 +1277,7 @@
         <v>-1055.950000000004</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>95504.67</v>
@@ -1415,7 +1415,7 @@
         <v>-2232.580000000006</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>97827.75999999998</v>
@@ -1461,7 +1461,7 @@
         <v>-995.6099999999949</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>96832.14999999999</v>
@@ -1507,7 +1507,7 @@
         <v>-301.7000000000043</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>96530.44999999998</v>
@@ -1645,7 +1645,7 @@
         <v>-995.6099999999949</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>106577.06</v>
